--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J05-SubjectRole-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J05-SubjectRole-CISIS.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="919">
   <si>
     <t>Property</t>
   </si>
@@ -46,7 +46,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251028120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -73,7 +73,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2473,12 +2473,6 @@
     <t>Préparateur en pharmacie (officine)</t>
   </si>
   <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>Auxiliaire de vie sociale</t>
-  </si>
-  <si>
     <t>319</t>
   </si>
   <si>
@@ -2501,12 +2495,6 @@
   </si>
   <si>
     <t>Assistant familial</t>
-  </si>
-  <si>
-    <t>323</t>
-  </si>
-  <si>
-    <t>Aide médico-psychologique (AMP)</t>
   </si>
   <si>
     <t>324</t>
@@ -3553,7 +3541,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4122,34 +4110,18 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>918</v>
+        <v>38</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>919</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>920</v>
+        <v>39</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>922</v>
+        <v>918</v>
       </c>
     </row>
   </sheetData>
